--- a/Results_experiment/exp_1/preds_1111114442222222.xlsx
+++ b/Results_experiment/exp_1/preds_1111114442222222.xlsx
@@ -1179,7 +1179,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D2">
-        <v>-2.30495285987854</v>
+        <v>-2.526097297668457</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1193,7 +1193,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D3">
-        <v>4.71819019317627</v>
+        <v>2.635987520217896</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1207,7 +1207,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D4">
-        <v>1.266409993171692</v>
+        <v>0.4319504797458649</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1221,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>-0.5698214769363403</v>
+        <v>-0.1977943181991577</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1235,7 +1235,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D6">
-        <v>4.032653331756592</v>
+        <v>3.176749467849731</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1249,7 +1249,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D7">
-        <v>3.92223334312439</v>
+        <v>3.540436506271362</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1263,7 +1263,7 @@
         <v>-7</v>
       </c>
       <c r="D8">
-        <v>-2.474299192428589</v>
+        <v>-2.855676174163818</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1277,7 +1277,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D9">
-        <v>8.907560348510742</v>
+        <v>8.849410057067871</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1291,7 +1291,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D10">
-        <v>7.38637113571167</v>
+        <v>6.646560668945312</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1305,7 +1305,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D11">
-        <v>-1.335836887359619</v>
+        <v>-1.53084659576416</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1319,7 +1319,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D12">
-        <v>-1.336383700370789</v>
+        <v>-1.415885448455811</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1333,7 +1333,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D13">
-        <v>9.95098876953125</v>
+        <v>9.910126686096191</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1347,7 +1347,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D14">
-        <v>-2.135157108306885</v>
+        <v>-3.602205038070679</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1361,7 +1361,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D15">
-        <v>1.905839800834656</v>
+        <v>1.869982004165649</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1375,7 +1375,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D16">
-        <v>2.845752239227295</v>
+        <v>2.545212030410767</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1389,7 +1389,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D17">
-        <v>-0.7681047916412354</v>
+        <v>-1.000664710998535</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1403,7 +1403,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D18">
-        <v>10.18553352355957</v>
+        <v>9.598016738891602</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1417,7 +1417,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D19">
-        <v>2.609493017196655</v>
+        <v>1.548230171203613</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1431,7 +1431,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D20">
-        <v>8.273547172546387</v>
+        <v>7.430288314819336</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1445,7 +1445,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D21">
-        <v>2.236260652542114</v>
+        <v>1.518206596374512</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1459,7 +1459,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D22">
-        <v>-1.257035493850708</v>
+        <v>-2.195918321609497</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1473,7 +1473,7 @@
         <v>-1</v>
       </c>
       <c r="D23">
-        <v>-0.8522627353668213</v>
+        <v>-1.416737079620361</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1487,7 +1487,7 @@
         <v>11.5</v>
       </c>
       <c r="D24">
-        <v>3.319576501846313</v>
+        <v>-0.8588855862617493</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1501,7 +1501,7 @@
         <v>-14.5</v>
       </c>
       <c r="D25">
-        <v>-4.909382820129395</v>
+        <v>-5.843809604644775</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>3.407513380050659</v>
+        <v>1.818637847900391</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1529,7 +1529,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D27">
-        <v>2.261246204376221</v>
+        <v>1.546510696411133</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1543,7 +1543,7 @@
         <v>26.89999961853027</v>
       </c>
       <c r="D28">
-        <v>16.96992683410645</v>
+        <v>17.07276916503906</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1557,7 +1557,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D29">
-        <v>3.697179794311523</v>
+        <v>2.952205419540405</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1571,7 +1571,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D30">
-        <v>1.634761810302734</v>
+        <v>1.644467830657959</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1585,7 +1585,7 @@
         <v>10.5</v>
       </c>
       <c r="D31">
-        <v>2.983915090560913</v>
+        <v>2.108839511871338</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1599,7 +1599,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D32">
-        <v>2.9732985496521</v>
+        <v>2.540853977203369</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1613,7 +1613,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D33">
-        <v>7.04828929901123</v>
+        <v>5.715253829956055</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1627,7 +1627,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D34">
-        <v>3.110518217086792</v>
+        <v>2.519033432006836</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1641,7 +1641,7 @@
         <v>-9.800000190734863</v>
       </c>
       <c r="D35">
-        <v>-0.8641101121902466</v>
+        <v>-4.249934196472168</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1655,7 +1655,7 @@
         <v>6.5</v>
       </c>
       <c r="D36">
-        <v>2.889639139175415</v>
+        <v>1.755894660949707</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1669,7 +1669,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D37">
-        <v>-3.844489812850952</v>
+        <v>-3.274137735366821</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1683,7 +1683,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D38">
-        <v>6.456618309020996</v>
+        <v>5.966418743133545</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1697,7 +1697,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D39">
-        <v>9.138203620910645</v>
+        <v>8.302495956420898</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1711,7 +1711,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D40">
-        <v>3.630524635314941</v>
+        <v>3.114250421524048</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1725,7 +1725,7 @@
         <v>1.5</v>
       </c>
       <c r="D41">
-        <v>4.594797134399414</v>
+        <v>3.491739273071289</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1739,7 +1739,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D42">
-        <v>-1.256190538406372</v>
+        <v>-1.298877716064453</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1753,7 +1753,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D43">
-        <v>-1.257790207862854</v>
+        <v>-1.890536546707153</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1767,7 +1767,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D44">
-        <v>-0.2171152830123901</v>
+        <v>-0.9875927567481995</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1781,7 +1781,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D45">
-        <v>6.115333080291748</v>
+        <v>3.249979496002197</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1795,7 +1795,7 @@
         <v>3.5</v>
       </c>
       <c r="D46">
-        <v>-0.6148291826248169</v>
+        <v>-0.7731530070304871</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1809,7 +1809,7 @@
         <v>0.5</v>
       </c>
       <c r="D47">
-        <v>-1.001846671104431</v>
+        <v>-1.454416275024414</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1823,7 +1823,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D48">
-        <v>-0.2868007123470306</v>
+        <v>-0.3280676007270813</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1837,7 +1837,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D49">
-        <v>3.902585744857788</v>
+        <v>1.742177724838257</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1851,7 +1851,7 @@
         <v>-14.69999980926514</v>
       </c>
       <c r="D50">
-        <v>-6.431754112243652</v>
+        <v>-6.043334007263184</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1865,7 +1865,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D51">
-        <v>-2.471075773239136</v>
+        <v>-2.651014089584351</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1879,7 +1879,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D52">
-        <v>-0.4250749051570892</v>
+        <v>-1.044471740722656</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1893,7 +1893,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D53">
-        <v>2.625210046768188</v>
+        <v>1.768517255783081</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1907,7 +1907,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D54">
-        <v>6.45365047454834</v>
+        <v>4.25832986831665</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1921,7 +1921,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D55">
-        <v>-0.251924604177475</v>
+        <v>1.730421781539917</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1935,7 +1935,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D56">
-        <v>0.3072479963302612</v>
+        <v>-0.7548690438270569</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1949,7 +1949,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D57">
-        <v>2.692188739776611</v>
+        <v>1.204052567481995</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1963,7 +1963,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D58">
-        <v>2.970234394073486</v>
+        <v>1.649824857711792</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1977,7 +1977,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D59">
-        <v>-1.923420310020447</v>
+        <v>-2.005752086639404</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1991,7 +1991,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D60">
-        <v>1.328878045082092</v>
+        <v>0.791761040687561</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2005,7 +2005,7 @@
         <v>-2</v>
       </c>
       <c r="D61">
-        <v>-0.3926723301410675</v>
+        <v>-0.5730831027030945</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2019,7 +2019,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D62">
-        <v>-4.54977560043335</v>
+        <v>-8.446629524230957</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2033,7 +2033,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D63">
-        <v>-1.991260886192322</v>
+        <v>-1.698788404464722</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2047,7 +2047,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D64">
-        <v>-1.534935832023621</v>
+        <v>-1.518068313598633</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2061,7 +2061,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D65">
-        <v>2.965257406234741</v>
+        <v>2.402103185653687</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2075,7 +2075,7 @@
         <v>-3.5</v>
       </c>
       <c r="D66">
-        <v>2.229067802429199</v>
+        <v>0.8144169449806213</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2089,7 +2089,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D67">
-        <v>-1.718250155448914</v>
+        <v>-1.565960645675659</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2103,7 +2103,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D68">
-        <v>1.727584481239319</v>
+        <v>1.657059907913208</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2117,7 +2117,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D69">
-        <v>-0.8871263265609741</v>
+        <v>-0.9722523093223572</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2131,7 +2131,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D70">
-        <v>0.8117908239364624</v>
+        <v>0.6773179173469543</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="D71">
-        <v>-1.301936984062195</v>
+        <v>-1.265684604644775</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2159,7 +2159,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D72">
-        <v>4.121962070465088</v>
+        <v>3.055406332015991</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2173,7 +2173,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D73">
-        <v>4.79358959197998</v>
+        <v>3.009681940078735</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2187,7 +2187,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D74">
-        <v>-2.994446277618408</v>
+        <v>-2.762197971343994</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2201,7 +2201,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D75">
-        <v>-0.6819695234298706</v>
+        <v>-1.719921350479126</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2215,7 +2215,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D76">
-        <v>6.404630661010742</v>
+        <v>7.361430168151855</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2229,7 +2229,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D77">
-        <v>4.898787975311279</v>
+        <v>4.289141178131104</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2243,7 +2243,7 @@
         <v>3.5</v>
       </c>
       <c r="D78">
-        <v>-2.266486406326294</v>
+        <v>-2.613248109817505</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2257,7 +2257,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D79">
-        <v>-0.7503621578216553</v>
+        <v>-1.281075954437256</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2271,7 +2271,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D80">
-        <v>2.478775501251221</v>
+        <v>1.639554738998413</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2285,7 +2285,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D81">
-        <v>-5.089273452758789</v>
+        <v>-4.88456916809082</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2299,7 +2299,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D82">
-        <v>5.178293228149414</v>
+        <v>4.070219993591309</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2313,7 +2313,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D83">
-        <v>-1.538917660713196</v>
+        <v>-1.433689117431641</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2327,7 +2327,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D84">
-        <v>-2.911908626556396</v>
+        <v>-2.515312194824219</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2341,7 +2341,7 @@
         <v>8</v>
       </c>
       <c r="D85">
-        <v>3.514500856399536</v>
+        <v>2.701477289199829</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2355,7 +2355,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D86">
-        <v>-0.8205399513244629</v>
+        <v>-1.546416997909546</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2369,7 +2369,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D87">
-        <v>-0.6452533006668091</v>
+        <v>-0.636172354221344</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2383,7 +2383,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D88">
-        <v>5.867703437805176</v>
+        <v>3.890726089477539</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2397,7 +2397,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D89">
-        <v>2.459589242935181</v>
+        <v>2.336823225021362</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2411,7 +2411,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D90">
-        <v>-1.74548614025116</v>
+        <v>-2.018362760543823</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2425,7 +2425,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D91">
-        <v>11.44855403900146</v>
+        <v>9.507586479187012</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2439,7 +2439,7 @@
         <v>-0.5</v>
       </c>
       <c r="D92">
-        <v>-3.804181337356567</v>
+        <v>-3.989088296890259</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2453,7 +2453,7 @@
         <v>4</v>
       </c>
       <c r="D93">
-        <v>6.576210498809814</v>
+        <v>5.036102294921875</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2467,7 +2467,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D94">
-        <v>0.9741886854171753</v>
+        <v>0.2454226911067963</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2481,7 +2481,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D95">
-        <v>-1.472277641296387</v>
+        <v>-1.174364805221558</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2495,7 +2495,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D96">
-        <v>3.594270944595337</v>
+        <v>2.872594594955444</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2509,7 +2509,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D97">
-        <v>6.317543029785156</v>
+        <v>4.71764087677002</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2523,7 +2523,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D98">
-        <v>6.372974395751953</v>
+        <v>7.162577629089355</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2537,7 +2537,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D99">
-        <v>1.536996245384216</v>
+        <v>2.26356840133667</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2551,7 +2551,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D100">
-        <v>-0.738794207572937</v>
+        <v>-3.610335111618042</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2565,7 +2565,7 @@
         <v>4.5</v>
       </c>
       <c r="D101">
-        <v>3.431151390075684</v>
+        <v>1.493135452270508</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2579,7 +2579,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D102">
-        <v>3.286231517791748</v>
+        <v>2.429326295852661</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2593,7 +2593,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D103">
-        <v>0.894235372543335</v>
+        <v>1.011780023574829</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2607,7 +2607,7 @@
         <v>10.5</v>
       </c>
       <c r="D104">
-        <v>4.21841287612915</v>
+        <v>3.785326480865479</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2621,7 +2621,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D105">
-        <v>0.3061354458332062</v>
+        <v>1.101247549057007</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2635,7 +2635,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D106">
-        <v>-0.9464658498764038</v>
+        <v>-1.077393293380737</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2649,7 +2649,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D107">
-        <v>9.477263450622559</v>
+        <v>8.958098411560059</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2663,7 +2663,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D108">
-        <v>6.414230346679688</v>
+        <v>5.747973442077637</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2677,7 +2677,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D109">
-        <v>8.391534805297852</v>
+        <v>7.8188157081604</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2691,7 +2691,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D110">
-        <v>5.607019424438477</v>
+        <v>3.895287990570068</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2705,7 +2705,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D111">
-        <v>-7.056705474853516</v>
+        <v>-7.051750183105469</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2719,7 +2719,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D112">
-        <v>-1.149978518486023</v>
+        <v>-1.073708534240723</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2733,7 +2733,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D113">
-        <v>-2.125916957855225</v>
+        <v>-2.354750871658325</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2747,7 +2747,7 @@
         <v>-1</v>
       </c>
       <c r="D114">
-        <v>-1.869260430335999</v>
+        <v>-2.716590642929077</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2761,7 +2761,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D115">
-        <v>2.157131910324097</v>
+        <v>2.193207740783691</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2775,7 +2775,7 @@
         <v>-20.29999923706055</v>
       </c>
       <c r="D116">
-        <v>-14.80203437805176</v>
+        <v>-14.8916072845459</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2789,7 +2789,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D117">
-        <v>0.2484010308980942</v>
+        <v>-1.040616273880005</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2803,7 +2803,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D118">
-        <v>-0.5431874990463257</v>
+        <v>-1.352200508117676</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2817,7 +2817,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D119">
-        <v>3.554840326309204</v>
+        <v>2.748961687088013</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2831,7 +2831,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D120">
-        <v>-3.798384428024292</v>
+        <v>-3.390063047409058</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2845,7 +2845,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D121">
-        <v>-0.5782480239868164</v>
+        <v>-1.76698637008667</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2859,7 +2859,7 @@
         <v>-20.10000038146973</v>
       </c>
       <c r="D122">
-        <v>-0.4411104619503021</v>
+        <v>-0.6195744872093201</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2873,7 +2873,7 @@
         <v>6.5</v>
       </c>
       <c r="D123">
-        <v>7.751398086547852</v>
+        <v>6.449636459350586</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2887,7 +2887,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D124">
-        <v>0.4243341088294983</v>
+        <v>1.074565172195435</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2901,7 +2901,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D125">
-        <v>-1.669311046600342</v>
+        <v>-1.738025665283203</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2915,7 +2915,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D126">
-        <v>-1.714998364448547</v>
+        <v>-1.978250741958618</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2929,7 +2929,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D127">
-        <v>3.837636709213257</v>
+        <v>3.023121118545532</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2943,7 +2943,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D128">
-        <v>2.17601490020752</v>
+        <v>1.316264152526855</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2957,7 +2957,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D129">
-        <v>2.954546451568604</v>
+        <v>2.113398313522339</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2971,7 +2971,7 @@
         <v>-0.5</v>
       </c>
       <c r="D130">
-        <v>-2.027620792388916</v>
+        <v>-2.209192514419556</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2985,7 +2985,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D131">
-        <v>2.215962171554565</v>
+        <v>1.51480507850647</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2999,7 +2999,7 @@
         <v>-2.5</v>
       </c>
       <c r="D132">
-        <v>-0.5998028516769409</v>
+        <v>-0.7557387948036194</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3013,7 +3013,7 @@
         <v>24.89999961853027</v>
       </c>
       <c r="D133">
-        <v>19.66929244995117</v>
+        <v>20.15317153930664</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3027,7 +3027,7 @@
         <v>0.5</v>
       </c>
       <c r="D134">
-        <v>2.633272171020508</v>
+        <v>2.134386777877808</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3041,7 +3041,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D135">
-        <v>6.41253137588501</v>
+        <v>6.639439105987549</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3055,7 +3055,7 @@
         <v>18.70000076293945</v>
       </c>
       <c r="D136">
-        <v>10.69514560699463</v>
+        <v>10.12777328491211</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3069,7 +3069,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D137">
-        <v>-0.9294027090072632</v>
+        <v>-0.853018581867218</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3083,7 +3083,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D138">
-        <v>4.436399459838867</v>
+        <v>3.967834234237671</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3097,7 +3097,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D139">
-        <v>-3.094138383865356</v>
+        <v>-2.112631559371948</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3111,7 +3111,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D140">
-        <v>2.129395246505737</v>
+        <v>2.174832105636597</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3125,7 +3125,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D141">
-        <v>6.584630012512207</v>
+        <v>6.445619583129883</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3139,7 +3139,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D142">
-        <v>0.1344670653343201</v>
+        <v>-0.4897114634513855</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3153,7 +3153,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D143">
-        <v>6.250524520874023</v>
+        <v>4.390944480895996</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3167,7 +3167,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D144">
-        <v>0.8532754182815552</v>
+        <v>-0.3568322658538818</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3181,7 +3181,7 @@
         <v>-2.5</v>
       </c>
       <c r="D145">
-        <v>-1.436462759971619</v>
+        <v>-1.664755821228027</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3195,7 +3195,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D146">
-        <v>6.975778579711914</v>
+        <v>5.078583240509033</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3209,7 +3209,7 @@
         <v>13.5</v>
       </c>
       <c r="D147">
-        <v>9.378363609313965</v>
+        <v>8.013025283813477</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3223,7 +3223,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D148">
-        <v>-3.724721670150757</v>
+        <v>-3.267633676528931</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3237,7 +3237,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D149">
-        <v>-0.511552095413208</v>
+        <v>0.4143051505088806</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3251,7 +3251,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D150">
-        <v>8.438721656799316</v>
+        <v>7.525790691375732</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3265,7 +3265,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D151">
-        <v>3.398850679397583</v>
+        <v>2.866841554641724</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3279,7 +3279,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D152">
-        <v>-0.2557643353939056</v>
+        <v>-0.624778687953949</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3293,7 +3293,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D153">
-        <v>5.65986442565918</v>
+        <v>2.282405376434326</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3307,7 +3307,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D154">
-        <v>-1.305243372917175</v>
+        <v>-1.21905517578125</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3321,7 +3321,7 @@
         <v>-1.5</v>
       </c>
       <c r="D155">
-        <v>-1.87287175655365</v>
+        <v>-1.563205718994141</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3335,7 +3335,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D156">
-        <v>3.83122706413269</v>
+        <v>2.915852785110474</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3349,7 +3349,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D157">
-        <v>-1.473831534385681</v>
+        <v>-1.969506502151489</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3363,7 +3363,7 @@
         <v>9</v>
       </c>
       <c r="D158">
-        <v>-1.262215733528137</v>
+        <v>-0.1390071213245392</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3377,7 +3377,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D159">
-        <v>-1.112295269966125</v>
+        <v>-1.842735767364502</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="D160">
-        <v>-1.560232281684875</v>
+        <v>-0.4699195623397827</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3405,7 +3405,7 @@
         <v>8</v>
       </c>
       <c r="D161">
-        <v>9.991244316101074</v>
+        <v>9.094401359558105</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3419,7 +3419,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D162">
-        <v>2.411146879196167</v>
+        <v>1.671546697616577</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3433,7 +3433,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D163">
-        <v>-0.5018137693405151</v>
+        <v>-1.976839065551758</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3447,7 +3447,7 @@
         <v>-0.5</v>
       </c>
       <c r="D164">
-        <v>-1.205392003059387</v>
+        <v>-1.176749229431152</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3461,7 +3461,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D165">
-        <v>0.8312101364135742</v>
+        <v>0.8096605539321899</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3475,7 +3475,7 @@
         <v>-4.5</v>
       </c>
       <c r="D166">
-        <v>-1.07821798324585</v>
+        <v>-2.948928833007812</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3489,7 +3489,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D167">
-        <v>2.181833028793335</v>
+        <v>1.101228713989258</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3503,7 +3503,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D168">
-        <v>8.619309425354004</v>
+        <v>7.677777290344238</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3517,7 +3517,7 @@
         <v>-1</v>
       </c>
       <c r="D169">
-        <v>-0.3827231824398041</v>
+        <v>-0.6936468482017517</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3531,7 +3531,7 @@
         <v>1.5</v>
       </c>
       <c r="D170">
-        <v>0.2411950379610062</v>
+        <v>-1.256714820861816</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3545,7 +3545,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D171">
-        <v>6.62705659866333</v>
+        <v>5.464953899383545</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3559,7 +3559,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D172">
-        <v>1.995110154151917</v>
+        <v>2.081178426742554</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3573,7 +3573,7 @@
         <v>10.5</v>
       </c>
       <c r="D173">
-        <v>8.80264949798584</v>
+        <v>8.143572807312012</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3587,7 +3587,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D174">
-        <v>1.79027533531189</v>
+        <v>1.243802309036255</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3601,7 +3601,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D175">
-        <v>5.262931823730469</v>
+        <v>4.925916194915771</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3615,7 +3615,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D176">
-        <v>2.098145008087158</v>
+        <v>1.531860828399658</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3629,7 +3629,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D177">
-        <v>-0.9946173429489136</v>
+        <v>-0.869964063167572</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3643,7 +3643,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D178">
-        <v>4.454780578613281</v>
+        <v>3.111891984939575</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3657,7 +3657,7 @@
         <v>-10.30000019073486</v>
       </c>
       <c r="D179">
-        <v>-5.444165229797363</v>
+        <v>-3.607955455780029</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3671,7 +3671,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>3.193037509918213</v>
+        <v>2.31604528427124</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3685,7 +3685,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D181">
-        <v>-0.3687605559825897</v>
+        <v>-0.6725881695747375</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>-2</v>
       </c>
       <c r="D182">
-        <v>-0.8909560441970825</v>
+        <v>-1.151125907897949</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3713,7 +3713,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D183">
-        <v>5.058506011962891</v>
+        <v>3.51523756980896</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3727,7 +3727,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D184">
-        <v>-4.382832527160645</v>
+        <v>-1.553711652755737</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3741,7 +3741,7 @@
         <v>-3</v>
       </c>
       <c r="D185">
-        <v>-2.12375807762146</v>
+        <v>-1.776179313659668</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3755,7 +3755,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D186">
-        <v>3.807969808578491</v>
+        <v>-0.3524092435836792</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3769,7 +3769,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D187">
-        <v>6.896206378936768</v>
+        <v>5.807873725891113</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3783,7 +3783,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D188">
-        <v>-0.6480180025100708</v>
+        <v>1.505315780639648</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3797,7 +3797,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D189">
-        <v>2.170811653137207</v>
+        <v>2.634680032730103</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3811,7 +3811,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D190">
-        <v>0.4968852996826172</v>
+        <v>-0.7254419922828674</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3825,7 +3825,7 @@
         <v>1.5</v>
       </c>
       <c r="D191">
-        <v>0.01225990056991577</v>
+        <v>-0.47198885679245</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3839,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="D192">
-        <v>2.31463623046875</v>
+        <v>-0.3634586930274963</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3853,7 +3853,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D193">
-        <v>4.57051944732666</v>
+        <v>3.041664361953735</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3867,7 +3867,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D194">
-        <v>8.984322547912598</v>
+        <v>8.481349945068359</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3881,7 +3881,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D195">
-        <v>7.123075485229492</v>
+        <v>5.572440147399902</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3895,7 +3895,7 @@
         <v>4</v>
       </c>
       <c r="D196">
-        <v>1.02571713924408</v>
+        <v>0.3679304420948029</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3909,7 +3909,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D197">
-        <v>5.436101913452148</v>
+        <v>4.131753444671631</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3923,7 +3923,7 @@
         <v>2.5</v>
       </c>
       <c r="D198">
-        <v>-0.5838838815689087</v>
+        <v>-0.7118837237358093</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3937,7 +3937,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D199">
-        <v>5.653872013092041</v>
+        <v>4.369879722595215</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3951,7 +3951,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D200">
-        <v>-0.3514581024646759</v>
+        <v>-0.6828315854072571</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3965,7 +3965,7 @@
         <v>-8.5</v>
       </c>
       <c r="D201">
-        <v>-0.9472635984420776</v>
+        <v>-2.161188840866089</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3979,7 +3979,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D202">
-        <v>5.380992889404297</v>
+        <v>3.734932899475098</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3993,7 +3993,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D203">
-        <v>-3.676710605621338</v>
+        <v>-3.474465370178223</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4007,7 +4007,7 @@
         <v>-1.5</v>
       </c>
       <c r="D204">
-        <v>1.327549457550049</v>
+        <v>1.720460891723633</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4021,7 +4021,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D205">
-        <v>10.91492176055908</v>
+        <v>10.8635368347168</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4035,7 +4035,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D206">
-        <v>4.860613346099854</v>
+        <v>2.650578737258911</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4049,7 +4049,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D207">
-        <v>-0.4929809272289276</v>
+        <v>-0.5801143050193787</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4063,7 +4063,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D208">
-        <v>-1.971944689750671</v>
+        <v>-2.214478969573975</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4077,7 +4077,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D209">
-        <v>-0.9701415300369263</v>
+        <v>-1.831745624542236</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4091,7 +4091,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D210">
-        <v>-0.3699922859668732</v>
+        <v>-0.5558710098266602</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4105,7 +4105,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D211">
-        <v>5.00706148147583</v>
+        <v>4.352021217346191</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4119,7 +4119,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D212">
-        <v>4.761479377746582</v>
+        <v>2.432976007461548</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4133,7 +4133,7 @@
         <v>1.5</v>
       </c>
       <c r="D213">
-        <v>2.309379816055298</v>
+        <v>1.244229793548584</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4147,7 +4147,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D214">
-        <v>9.611641883850098</v>
+        <v>8.455798149108887</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4161,7 +4161,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D215">
-        <v>-2.095977067947388</v>
+        <v>-2.548320055007935</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4175,7 +4175,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D216">
-        <v>2.510385274887085</v>
+        <v>1.791222095489502</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4189,7 +4189,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D217">
-        <v>-1.908932328224182</v>
+        <v>-1.471683740615845</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4203,7 +4203,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D218">
-        <v>8.336121559143066</v>
+        <v>7.301029205322266</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4217,7 +4217,7 @@
         <v>-4.5</v>
       </c>
       <c r="D219">
-        <v>-4.798524856567383</v>
+        <v>-3.814565896987915</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4231,7 +4231,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D220">
-        <v>0.9525749683380127</v>
+        <v>0.4057612419128418</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4245,7 +4245,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D221">
-        <v>6.298230648040771</v>
+        <v>5.265495300292969</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4259,7 +4259,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D222">
-        <v>8.428465843200684</v>
+        <v>6.649588108062744</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4273,7 +4273,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D223">
-        <v>-0.7836889028549194</v>
+        <v>-1.045819044113159</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4287,7 +4287,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D224">
-        <v>-3.880867719650269</v>
+        <v>-3.198116540908813</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4301,7 +4301,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D225">
-        <v>-2.780041933059692</v>
+        <v>-2.68619179725647</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4315,7 +4315,7 @@
         <v>-3</v>
       </c>
       <c r="D226">
-        <v>-1.866209149360657</v>
+        <v>-2.46517276763916</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4329,7 +4329,7 @@
         <v>-1</v>
       </c>
       <c r="D227">
-        <v>-0.9843283891677856</v>
+        <v>-0.9682309031486511</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4343,7 +4343,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D228">
-        <v>-1.320911645889282</v>
+        <v>-1.565735340118408</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4357,7 +4357,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D229">
-        <v>7.044464111328125</v>
+        <v>5.704558372497559</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4371,7 +4371,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D230">
-        <v>4.66093921661377</v>
+        <v>1.290081024169922</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4385,7 +4385,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D231">
-        <v>0.3146526217460632</v>
+        <v>-0.6656275987625122</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4399,7 +4399,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D232">
-        <v>6.777172565460205</v>
+        <v>7.604369163513184</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4413,7 +4413,7 @@
         <v>-11.10000038146973</v>
       </c>
       <c r="D233">
-        <v>-2.427417516708374</v>
+        <v>-2.100915670394897</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4427,7 +4427,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D234">
-        <v>-2.121799230575562</v>
+        <v>-1.957653045654297</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4441,7 +4441,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D235">
-        <v>4.171718120574951</v>
+        <v>2.401103258132935</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4455,7 +4455,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D236">
-        <v>4.346239566802979</v>
+        <v>2.389442682266235</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4469,7 +4469,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D237">
-        <v>-1.532859444618225</v>
+        <v>-0.9461234211921692</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4483,7 +4483,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D238">
-        <v>-2.121899366378784</v>
+        <v>-1.494885444641113</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4497,7 +4497,7 @@
         <v>3.5</v>
       </c>
       <c r="D239">
-        <v>4.130130290985107</v>
+        <v>3.664803504943848</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4511,7 +4511,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D240">
-        <v>1.252541065216064</v>
+        <v>-0.4967107176780701</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4525,7 +4525,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D241">
-        <v>-0.5721837282180786</v>
+        <v>-0.5432539582252502</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4539,7 +4539,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D242">
-        <v>-0.5946542024612427</v>
+        <v>-0.7805960774421692</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4553,7 +4553,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D243">
-        <v>0.59654700756073</v>
+        <v>-1.111968517303467</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4567,7 +4567,7 @@
         <v>5</v>
       </c>
       <c r="D244">
-        <v>4.88310432434082</v>
+        <v>4.268880367279053</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4581,7 +4581,7 @@
         <v>15.89999961853027</v>
       </c>
       <c r="D245">
-        <v>12.18841457366943</v>
+        <v>10.0339241027832</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4595,7 +4595,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D246">
-        <v>5.433363914489746</v>
+        <v>5.642163753509521</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4609,7 +4609,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D247">
-        <v>-1.425224661827087</v>
+        <v>-1.48155403137207</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4623,7 +4623,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D248">
-        <v>4.802809715270996</v>
+        <v>4.0526442527771</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4637,7 +4637,7 @@
         <v>-6.5</v>
       </c>
       <c r="D249">
-        <v>-2.851595640182495</v>
+        <v>-2.771602392196655</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4651,7 +4651,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D250">
-        <v>-0.5261927843093872</v>
+        <v>-1.487871646881104</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4665,7 +4665,7 @@
         <v>-2.5</v>
       </c>
       <c r="D251">
-        <v>-0.509799599647522</v>
+        <v>-0.7682607769966125</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4679,7 +4679,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D252">
-        <v>-1.248354315757751</v>
+        <v>-1.650610446929932</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4693,7 +4693,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D253">
-        <v>2.472972869873047</v>
+        <v>1.64875340461731</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4707,7 +4707,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>5.163183212280273</v>
+        <v>4.427866458892822</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4721,7 +4721,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D255">
-        <v>-2.803755044937134</v>
+        <v>-3.399917602539062</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4735,7 +4735,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D256">
-        <v>2.304115533828735</v>
+        <v>2.030124664306641</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4749,7 +4749,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D257">
-        <v>2.107089042663574</v>
+        <v>0.06180089712142944</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4763,7 +4763,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D258">
-        <v>-0.9055880308151245</v>
+        <v>-0.8731291890144348</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4777,7 +4777,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D259">
-        <v>-0.8422418832778931</v>
+        <v>-1.387658834457397</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4791,7 +4791,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D260">
-        <v>-0.8620686531066895</v>
+        <v>-1.192816257476807</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4805,7 +4805,7 @@
         <v>9.5</v>
       </c>
       <c r="D261">
-        <v>4.952734470367432</v>
+        <v>3.765275239944458</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4819,7 +4819,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D262">
-        <v>-2.485702276229858</v>
+        <v>-2.62544846534729</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4833,7 +4833,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D263">
-        <v>0.7540509700775146</v>
+        <v>0.2693577408790588</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4847,7 +4847,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D264">
-        <v>5.022845268249512</v>
+        <v>4.09285831451416</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4861,7 +4861,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D265">
-        <v>-0.4273061454296112</v>
+        <v>-1.94805383682251</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4875,7 +4875,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D266">
-        <v>4.769946098327637</v>
+        <v>4.23838996887207</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4889,7 +4889,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D267">
-        <v>-2.286573171615601</v>
+        <v>-2.549975633621216</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4903,7 +4903,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D268">
-        <v>-2.015029430389404</v>
+        <v>-1.217057943344116</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4917,7 +4917,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D269">
-        <v>8.167018890380859</v>
+        <v>6.746743202209473</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4931,7 +4931,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D270">
-        <v>-1.173583030700684</v>
+        <v>-1.631359100341797</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4945,7 +4945,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D271">
-        <v>1.798849582672119</v>
+        <v>1.664918899536133</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4959,7 +4959,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D272">
-        <v>-0.6999801397323608</v>
+        <v>-0.331065833568573</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4973,7 +4973,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D273">
-        <v>4.775157928466797</v>
+        <v>2.408179998397827</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4987,7 +4987,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D274">
-        <v>6.03172779083252</v>
+        <v>4.129912376403809</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5001,7 +5001,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D275">
-        <v>-1.692977786064148</v>
+        <v>-1.931636571884155</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5015,7 +5015,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D276">
-        <v>-0.4002250134944916</v>
+        <v>-1.823490619659424</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5029,7 +5029,7 @@
         <v>8.5</v>
       </c>
       <c r="D277">
-        <v>7.632045269012451</v>
+        <v>6.47007942199707</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5043,7 +5043,7 @@
         <v>0.5</v>
       </c>
       <c r="D278">
-        <v>5.090765476226807</v>
+        <v>4.311704158782959</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5057,7 +5057,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D279">
-        <v>-8.400582313537598</v>
+        <v>-6.725175857543945</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5071,7 +5071,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D280">
-        <v>1.868695497512817</v>
+        <v>0.4255247712135315</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5085,7 +5085,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D281">
-        <v>2.441490411758423</v>
+        <v>2.11149787902832</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5099,7 +5099,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D282">
-        <v>-0.6224441528320312</v>
+        <v>-0.4785585999488831</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5113,7 +5113,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D283">
-        <v>2.445017337799072</v>
+        <v>2.675319910049438</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5127,7 +5127,7 @@
         <v>35.70000076293945</v>
       </c>
       <c r="D284">
-        <v>26.44915962219238</v>
+        <v>25.44362449645996</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5141,7 +5141,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D285">
-        <v>3.492960453033447</v>
+        <v>2.835049390792847</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5155,7 +5155,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D286">
-        <v>11.66023349761963</v>
+        <v>9.522281646728516</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5169,7 +5169,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D287">
-        <v>-0.151443213224411</v>
+        <v>-1.059305429458618</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5183,7 +5183,7 @@
         <v>2</v>
       </c>
       <c r="D288">
-        <v>1.551733136177063</v>
+        <v>2.201259851455688</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5197,7 +5197,7 @@
         <v>-0.5</v>
       </c>
       <c r="D289">
-        <v>-0.6887427568435669</v>
+        <v>-0.2241731286048889</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5211,7 +5211,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D290">
-        <v>-0.962024450302124</v>
+        <v>-1.988694190979004</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5225,7 +5225,7 @@
         <v>-1.5</v>
       </c>
       <c r="D291">
-        <v>-1.153957843780518</v>
+        <v>-1.058208227157593</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5239,7 +5239,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D292">
-        <v>-0.3304602205753326</v>
+        <v>-0.6768850684165955</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5253,7 +5253,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D293">
-        <v>-0.5172382593154907</v>
+        <v>0.03910815715789795</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5267,7 +5267,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D294">
-        <v>-0.7595313787460327</v>
+        <v>-0.829031765460968</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5281,7 +5281,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D295">
-        <v>1.967166543006897</v>
+        <v>0.3302866816520691</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5295,7 +5295,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D296">
-        <v>0.9848183393478394</v>
+        <v>1.489016532897949</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5309,7 +5309,7 @@
         <v>-15.69999980926514</v>
       </c>
       <c r="D297">
-        <v>-9.177731513977051</v>
+        <v>-9.411802291870117</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5323,7 +5323,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D298">
-        <v>4.818978309631348</v>
+        <v>3.858211278915405</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5337,7 +5337,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D299">
-        <v>9.635937690734863</v>
+        <v>8.641241073608398</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5351,7 +5351,7 @@
         <v>-1</v>
       </c>
       <c r="D300">
-        <v>-1.081906676292419</v>
+        <v>-1.558163404464722</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5365,7 +5365,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D301">
-        <v>9.009991645812988</v>
+        <v>8.559806823730469</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5379,7 +5379,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D302">
-        <v>1.560753226280212</v>
+        <v>1.21387767791748</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5393,7 +5393,7 @@
         <v>11</v>
       </c>
       <c r="D303">
-        <v>5.552898406982422</v>
+        <v>3.637578725814819</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5407,7 +5407,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D304">
-        <v>-3.595067501068115</v>
+        <v>-3.410500764846802</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5421,7 +5421,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D305">
-        <v>1.843818545341492</v>
+        <v>1.516740322113037</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5435,7 +5435,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D306">
-        <v>4.210549354553223</v>
+        <v>1.648207664489746</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5449,7 +5449,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D307">
-        <v>-0.2020023167133331</v>
+        <v>-0.4517161846160889</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5463,7 +5463,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D308">
-        <v>-1.192301273345947</v>
+        <v>-1.25550651550293</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5477,7 +5477,7 @@
         <v>-1.5</v>
       </c>
       <c r="D309">
-        <v>-2.085503101348877</v>
+        <v>-2.334670543670654</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5491,7 +5491,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D310">
-        <v>2.787374496459961</v>
+        <v>1.874613761901855</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5505,7 +5505,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D311">
-        <v>0.2527090013027191</v>
+        <v>-0.5051763653755188</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5519,7 +5519,7 @@
         <v>-1</v>
       </c>
       <c r="D312">
-        <v>-0.6355141401290894</v>
+        <v>-0.3353434801101685</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5533,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="D313">
-        <v>4.284814357757568</v>
+        <v>3.673718690872192</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5547,7 +5547,7 @@
         <v>2.5</v>
       </c>
       <c r="D314">
-        <v>3.054886817932129</v>
+        <v>2.595674276351929</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5561,7 +5561,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D315">
-        <v>3.725590944290161</v>
+        <v>2.748532295227051</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5575,7 +5575,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D316">
-        <v>-1.736765503883362</v>
+        <v>-1.709086418151855</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5589,7 +5589,7 @@
         <v>7.5</v>
       </c>
       <c r="D317">
-        <v>2.940229654312134</v>
+        <v>2.359379529953003</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5603,7 +5603,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D318">
-        <v>-1.211444854736328</v>
+        <v>-1.108582019805908</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5617,7 +5617,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D319">
-        <v>2.696077585220337</v>
+        <v>2.346789360046387</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5631,7 +5631,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D320">
-        <v>7.735971450805664</v>
+        <v>7.05243968963623</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5645,7 +5645,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D321">
-        <v>-0.9381951093673706</v>
+        <v>-2.853756427764893</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5659,7 +5659,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D322">
-        <v>2.298984527587891</v>
+        <v>2.142423868179321</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5673,7 +5673,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D323">
-        <v>-2.462315320968628</v>
+        <v>-2.111990690231323</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5687,7 +5687,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D324">
-        <v>4.078126430511475</v>
+        <v>3.90155553817749</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5701,7 +5701,7 @@
         <v>7.5</v>
       </c>
       <c r="D325">
-        <v>5.072416305541992</v>
+        <v>3.925151109695435</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5715,7 +5715,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D326">
-        <v>-0.7210497856140137</v>
+        <v>-0.7949932217597961</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5729,7 +5729,7 @@
         <v>-23.20000076293945</v>
       </c>
       <c r="D327">
-        <v>-1.130358099937439</v>
+        <v>-0.5699049830436707</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5743,7 +5743,7 @@
         <v>-1</v>
       </c>
       <c r="D328">
-        <v>-0.5223894119262695</v>
+        <v>-0.322144091129303</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5757,7 +5757,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D329">
-        <v>-0.7215257883071899</v>
+        <v>-1.487870693206787</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5771,7 +5771,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D330">
-        <v>-7.116481781005859</v>
+        <v>-4.627357959747314</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5785,7 +5785,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D331">
-        <v>1.944137454032898</v>
+        <v>2.049777269363403</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5799,7 +5799,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D332">
-        <v>2.237860441207886</v>
+        <v>2.137145042419434</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5813,7 +5813,7 @@
         <v>11</v>
       </c>
       <c r="D333">
-        <v>3.023817777633667</v>
+        <v>2.106836080551147</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5827,7 +5827,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D334">
-        <v>-9.040666580200195</v>
+        <v>-10.26412200927734</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5841,7 +5841,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D335">
-        <v>4.723849296569824</v>
+        <v>4.099669933319092</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5855,7 +5855,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D336">
-        <v>-0.1798267066478729</v>
+        <v>-1.511434316635132</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5869,7 +5869,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D337">
-        <v>4.919374465942383</v>
+        <v>3.446575403213501</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5883,7 +5883,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D338">
-        <v>3.945449352264404</v>
+        <v>1.98556923866272</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5897,7 +5897,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D339">
-        <v>10.82692623138428</v>
+        <v>10.08436393737793</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5911,7 +5911,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D340">
-        <v>0.2857358455657959</v>
+        <v>0.4496709406375885</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5925,7 +5925,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D341">
-        <v>2.890638113021851</v>
+        <v>1.746058225631714</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5939,7 +5939,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D342">
-        <v>-2.749536752700806</v>
+        <v>-2.960218191146851</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5953,7 +5953,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D343">
-        <v>1.494064688682556</v>
+        <v>2.395391941070557</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5967,7 +5967,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D344">
-        <v>-0.9795125722885132</v>
+        <v>-0.6020295023918152</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5981,7 +5981,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D345">
-        <v>6.293401718139648</v>
+        <v>5.644935607910156</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5995,7 +5995,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D346">
-        <v>5.081542015075684</v>
+        <v>3.627410173416138</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6009,7 +6009,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D347">
-        <v>-8.489302635192871</v>
+        <v>-2.242536544799805</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6023,7 +6023,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D348">
-        <v>5.500858783721924</v>
+        <v>5.46399450302124</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6037,7 +6037,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D349">
-        <v>1.197972297668457</v>
+        <v>-0.7902677655220032</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6051,7 +6051,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D350">
-        <v>5.80233097076416</v>
+        <v>5.213847160339355</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6065,7 +6065,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D351">
-        <v>0.3346202969551086</v>
+        <v>0.9805880784988403</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6079,7 +6079,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D352">
-        <v>2.383067846298218</v>
+        <v>1.309087991714478</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6093,7 +6093,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D353">
-        <v>-14.92369651794434</v>
+        <v>-12.472731590271</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6107,7 +6107,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D354">
-        <v>-0.8650113344192505</v>
+        <v>-1.451901197433472</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6121,7 +6121,7 @@
         <v>15.5</v>
       </c>
       <c r="D355">
-        <v>8.634105682373047</v>
+        <v>9.568706512451172</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6135,7 +6135,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D356">
-        <v>-0.3887495100498199</v>
+        <v>-0.7320340275764465</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6149,7 +6149,7 @@
         <v>1.5</v>
       </c>
       <c r="D357">
-        <v>4.675320625305176</v>
+        <v>4.307780265808105</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6163,7 +6163,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D358">
-        <v>3.055115699768066</v>
+        <v>2.112188577651978</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6177,7 +6177,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D359">
-        <v>4.75911808013916</v>
+        <v>4.528083801269531</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6191,7 +6191,7 @@
         <v>5.5</v>
       </c>
       <c r="D360">
-        <v>2.666639804840088</v>
+        <v>1.752221822738647</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6205,7 +6205,7 @@
         <v>-1</v>
       </c>
       <c r="D361">
-        <v>0.5757508277893066</v>
+        <v>-0.6931465268135071</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6219,7 +6219,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D362">
-        <v>-2.671088457107544</v>
+        <v>-3.416562795639038</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6233,7 +6233,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D363">
-        <v>10.69947719573975</v>
+        <v>12.07567501068115</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6247,7 +6247,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D364">
-        <v>-2.052094221115112</v>
+        <v>-1.900630474090576</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6261,7 +6261,7 @@
         <v>1.5</v>
       </c>
       <c r="D365">
-        <v>2.312899112701416</v>
+        <v>1.157870769500732</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6275,7 +6275,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D366">
-        <v>0.6718075275421143</v>
+        <v>0.7421371936798096</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6289,7 +6289,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D367">
-        <v>-3.805390119552612</v>
+        <v>-2.953129053115845</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6303,7 +6303,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D368">
-        <v>9.726635932922363</v>
+        <v>7.597701072692871</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6317,7 +6317,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D369">
-        <v>-0.7229841947555542</v>
+        <v>-0.7671759724617004</v>
       </c>
     </row>
   </sheetData>
